--- a/For Software (Advances for New deal).xlsx
+++ b/For Software (Advances for New deal).xlsx
@@ -5,16 +5,16 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASK MARKETING\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UH_CRM\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7755"/>
+    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="20496" windowHeight="7752"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="152511" iterate="1"/>
+  <calcPr calcId="162913" iterate="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -396,7 +396,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -644,9 +644,6 @@
   </cellStyleXfs>
   <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -705,6 +702,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="9" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1141,622 +1141,622 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G58"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
     <col min="2" max="2" width="21" customWidth="1"/>
-    <col min="3" max="3" width="13.85546875" customWidth="1"/>
-    <col min="4" max="4" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.88671875" customWidth="1"/>
+    <col min="4" max="4" width="16.33203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="21" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="16" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="31.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="31.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.35">
+      <c r="A1" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-    </row>
-    <row r="2" spans="1:7" ht="19.5" x14ac:dyDescent="0.4">
-      <c r="A2" s="2" t="s">
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+    </row>
+    <row r="2" spans="1:7" ht="18.600000000000001" x14ac:dyDescent="0.45">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="6"/>
-    </row>
-    <row r="3" spans="1:7" ht="20.25" x14ac:dyDescent="0.4">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="7">
+      <c r="B2" s="1"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="5"/>
+    </row>
+    <row r="3" spans="1:7" ht="19.2" x14ac:dyDescent="0.45">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="6">
         <f>SUM(E5:E11)</f>
         <v>38250000</v>
       </c>
-      <c r="F3" s="6"/>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="8" t="s">
+      <c r="F3" s="5"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="E4" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="F4" s="7" t="s">
         <v>7</v>
       </c>
       <c r="G4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="10">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="9">
         <v>46156</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="8">
+      <c r="C5" s="7">
         <v>12900</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="E5" s="11">
+      <c r="E5" s="10">
         <v>3000000</v>
       </c>
-      <c r="F5" s="8" t="s">
+      <c r="F5" s="7" t="s">
         <v>11</v>
       </c>
       <c r="G5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="10">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="9">
         <v>46156</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="8">
+      <c r="C6" s="7">
         <v>12911</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="11">
+      <c r="E6" s="10">
         <v>3000000</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="F6" s="7" t="s">
         <v>11</v>
       </c>
       <c r="G6" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="10">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="9">
         <v>46160</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="8">
+      <c r="C7" s="7">
         <v>13206</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="E7" s="11">
+      <c r="E7" s="10">
         <v>6000000</v>
       </c>
-      <c r="F7" s="8" t="s">
+      <c r="F7" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="G7" s="12" t="s">
+      <c r="G7" s="11" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="10">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="9">
         <v>46161</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="8">
+      <c r="C8" s="7">
         <v>13255</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="E8" s="11">
+      <c r="E8" s="10">
         <v>5000000</v>
       </c>
-      <c r="F8" s="8" t="s">
+      <c r="F8" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="G8" s="12" t="s">
+      <c r="G8" s="11" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="10">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="9">
         <v>46161</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="8">
+      <c r="C9" s="7">
         <v>13349</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="E9" s="11">
+      <c r="E9" s="10">
         <v>5000000</v>
       </c>
-      <c r="F9" s="8" t="s">
+      <c r="F9" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="G9" s="12" t="s">
+      <c r="G9" s="11" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="10">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" s="9">
         <v>46163</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="8">
+      <c r="C10" s="7">
         <v>133558</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="D10" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="E10" s="11">
+      <c r="E10" s="10">
         <v>2250000</v>
       </c>
-      <c r="F10" s="8" t="s">
+      <c r="F10" s="7" t="s">
         <v>11</v>
       </c>
       <c r="G10" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="10">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="9">
         <v>46164</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="8">
+      <c r="C11" s="7">
         <v>13732</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="D11" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="E11" s="11">
+      <c r="E11" s="10">
         <v>14000000</v>
       </c>
-      <c r="F11" s="8" t="s">
+      <c r="F11" s="7" t="s">
         <v>11</v>
       </c>
       <c r="G11" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="8"/>
-      <c r="B12" s="8"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="8"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="8"/>
-      <c r="B13" s="8"/>
-      <c r="C13" s="8"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="8"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="8"/>
-      <c r="B14" s="8"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="11"/>
-      <c r="F14" s="8"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="13">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="7"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="10"/>
+      <c r="F12" s="7"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" s="7"/>
+      <c r="B13" s="7"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="10"/>
+      <c r="F13" s="7"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" s="7"/>
+      <c r="B14" s="7"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="10"/>
+      <c r="F14" s="7"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" s="12">
         <v>46155</v>
       </c>
-      <c r="B15" s="14" t="s">
+      <c r="B15" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14" t="s">
+      <c r="C15" s="13"/>
+      <c r="D15" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="E15" s="15">
+      <c r="E15" s="14">
         <v>9000000</v>
       </c>
-      <c r="F15" s="14"/>
-      <c r="G15" s="16" t="s">
+      <c r="F15" s="13"/>
+      <c r="G15" s="15" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="17" t="s">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="B16" s="14" t="s">
+      <c r="B16" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14" t="s">
+      <c r="C16" s="13"/>
+      <c r="D16" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="E16" s="15">
+      <c r="E16" s="14">
         <v>40000000</v>
       </c>
-      <c r="F16" s="14"/>
-      <c r="G16" s="16" t="s">
+      <c r="F16" s="13"/>
+      <c r="G16" s="15" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E17" s="18"/>
-    </row>
-    <row r="18" spans="1:5" ht="19.5" x14ac:dyDescent="0.4">
-      <c r="E18" s="19">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E17" s="17"/>
+    </row>
+    <row r="18" spans="1:5" ht="18.600000000000001" x14ac:dyDescent="0.45">
+      <c r="E18" s="18">
         <f>SUM(E15:E16)</f>
         <v>49000000</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E19" s="18"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E21" s="18"/>
-    </row>
-    <row r="22" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A22" s="20" t="s">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E19" s="17"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E21" s="17"/>
+    </row>
+    <row r="22" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A22" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="B22" s="20"/>
-      <c r="C22" s="21"/>
-    </row>
-    <row r="23" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A23" s="22" t="s">
+      <c r="B22" s="19"/>
+      <c r="C22" s="20"/>
+    </row>
+    <row r="23" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A23" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="B23" s="22" t="s">
+      <c r="B23" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="C23" s="23" t="s">
+      <c r="C23" s="22" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A24" s="24">
+    <row r="24" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A24" s="23">
         <v>1</v>
       </c>
       <c r="B24" t="s">
         <v>34</v>
       </c>
-      <c r="C24" s="25">
+      <c r="C24" s="24">
         <v>3000000</v>
       </c>
       <c r="D24" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A25" s="24">
+    <row r="25" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A25" s="23">
         <v>2</v>
       </c>
       <c r="B25" t="s">
         <v>36</v>
       </c>
-      <c r="C25" s="25">
+      <c r="C25" s="24">
         <v>5000000</v>
       </c>
       <c r="D25" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A26" s="24">
+    <row r="26" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A26" s="23">
         <v>3</v>
       </c>
       <c r="B26" t="s">
         <v>38</v>
       </c>
-      <c r="C26" s="25">
+      <c r="C26" s="24">
         <v>1000000</v>
       </c>
-      <c r="D26" s="26" t="s">
+      <c r="D26" s="25" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="27"/>
-      <c r="C27" s="28"/>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C28" s="28"/>
-    </row>
-    <row r="29" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B29" s="29" t="s">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27" s="26"/>
+      <c r="C27" s="27"/>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C28" s="27"/>
+    </row>
+    <row r="29" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B29" s="28" t="s">
         <v>40</v>
       </c>
-      <c r="C29" s="30">
+      <c r="C29" s="29">
         <f>SUM(C24:C25)</f>
         <v>8000000</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A31" s="31" t="s">
+    <row r="31" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A31" s="30" t="s">
         <v>33</v>
       </c>
-      <c r="B31" s="31" t="s">
+      <c r="B31" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="C31" s="31" t="s">
+      <c r="C31" s="30" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A32" s="24">
+    <row r="32" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A32" s="23">
         <v>1</v>
       </c>
-      <c r="B32" s="32" t="s">
+      <c r="B32" s="31" t="s">
         <v>41</v>
       </c>
-      <c r="C32" s="25">
+      <c r="C32" s="24">
         <v>1000000</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A33" s="24">
+    <row r="33" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A33" s="23">
         <v>2</v>
       </c>
-      <c r="B33" s="33" t="s">
+      <c r="B33" s="32" t="s">
         <v>26</v>
       </c>
-      <c r="C33" s="25">
+      <c r="C33" s="24">
         <v>14000000</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" s="24">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A34" s="23">
         <v>3</v>
       </c>
-      <c r="C34" s="28"/>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" s="24">
+      <c r="C34" s="27"/>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A35" s="23">
         <v>4</v>
       </c>
-      <c r="C35" s="18"/>
-    </row>
-    <row r="36" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A36" s="24"/>
-      <c r="B36" s="29" t="s">
+      <c r="C35" s="17"/>
+    </row>
+    <row r="36" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A36" s="23"/>
+      <c r="B36" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="C36" s="30">
+      <c r="C36" s="29">
         <f>SUM(C32:C34)</f>
         <v>15000000</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A38" s="31" t="s">
+    <row r="38" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A38" s="30" t="s">
         <v>33</v>
       </c>
-      <c r="B38" s="31" t="s">
+      <c r="B38" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="C38" s="31" t="s">
+      <c r="C38" s="30" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="39" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A39" s="24">
+    <row r="39" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A39" s="23">
         <v>1</v>
       </c>
-      <c r="B39" s="32" t="s">
+      <c r="B39" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="C39" s="25">
+      <c r="C39" s="24">
         <v>5000000</v>
       </c>
       <c r="D39" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="40" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A40" s="24">
+    <row r="40" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A40" s="23">
         <v>2</v>
       </c>
-      <c r="B40" s="12" t="s">
+      <c r="B40" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="C40" s="34">
+      <c r="C40" s="33">
         <v>5000000</v>
       </c>
       <c r="D40" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="41" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A41" s="24">
+    <row r="41" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A41" s="23">
         <v>3</v>
       </c>
       <c r="B41" t="s">
         <v>47</v>
       </c>
-      <c r="C41" s="25">
+      <c r="C41" s="24">
         <v>700000</v>
       </c>
-      <c r="D41" s="26" t="s">
+      <c r="D41" s="25" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42" s="24"/>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43" s="24"/>
-    </row>
-    <row r="44" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B44" s="35" t="s">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A42" s="23"/>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A43" s="23"/>
+    </row>
+    <row r="44" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B44" s="34" t="s">
         <v>49</v>
       </c>
-      <c r="C44" s="30">
+      <c r="C44" s="29">
         <f>SUM(C39:C40)</f>
         <v>10000000</v>
       </c>
     </row>
-    <row r="46" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A46" s="31" t="s">
+    <row r="46" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A46" s="30" t="s">
         <v>33</v>
       </c>
-      <c r="B46" s="31" t="s">
+      <c r="B46" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="C46" s="31" t="s">
+      <c r="C46" s="30" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="47" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A47" s="24">
+    <row r="47" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A47" s="23">
         <v>1</v>
       </c>
       <c r="B47" t="s">
         <v>50</v>
       </c>
-      <c r="C47" s="25">
+      <c r="C47" s="24">
         <v>3000000</v>
       </c>
     </row>
-    <row r="48" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A48" s="24">
+    <row r="48" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A48" s="23">
         <v>2</v>
       </c>
-      <c r="B48" s="32" t="s">
+      <c r="B48" s="31" t="s">
         <v>51</v>
       </c>
-      <c r="C48" s="25">
+      <c r="C48" s="24">
         <v>2250000</v>
       </c>
     </row>
-    <row r="49" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A49" s="24">
+    <row r="49" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A49" s="23">
         <v>3</v>
       </c>
-      <c r="B49" s="36" t="s">
+      <c r="B49" s="35" t="s">
         <v>52</v>
       </c>
-      <c r="C49" s="25">
+      <c r="C49" s="24">
         <v>1000000</v>
       </c>
-      <c r="D49" s="26" t="s">
+      <c r="D49" s="25" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="50" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A50" s="24">
+    <row r="50" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A50" s="23">
         <v>4</v>
       </c>
-      <c r="B50" s="36" t="s">
+      <c r="B50" s="35" t="s">
         <v>54</v>
       </c>
-      <c r="C50" s="25">
+      <c r="C50" s="24">
         <v>200000</v>
       </c>
-      <c r="D50" s="26" t="s">
+      <c r="D50" s="25" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="51" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A51" s="24">
+    <row r="51" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A51" s="23">
         <v>5</v>
       </c>
       <c r="B51" t="s">
         <v>55</v>
       </c>
-      <c r="C51" s="37">
+      <c r="C51" s="36">
         <v>200000</v>
       </c>
-      <c r="D51" s="26" t="s">
+      <c r="D51" s="25" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="52" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A52" s="24">
+    <row r="52" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A52" s="23">
         <v>6</v>
       </c>
       <c r="B52" t="s">
         <v>55</v>
       </c>
-      <c r="C52" s="37">
+      <c r="C52" s="36">
         <v>100000</v>
       </c>
-      <c r="D52" s="26" t="s">
+      <c r="D52" s="25" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A53" s="24"/>
-    </row>
-    <row r="54" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B54" s="35" t="s">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A53" s="23"/>
+    </row>
+    <row r="54" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B54" s="34" t="s">
         <v>57</v>
       </c>
-      <c r="C54" s="30">
+      <c r="C54" s="29">
         <f>SUM(C47:C48)</f>
         <v>5250000</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B55" s="38" t="s">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B55" s="37" t="s">
         <v>58</v>
       </c>
-      <c r="C55" s="39">
+      <c r="C55" s="38">
         <f>SUM(C47:C52)</f>
         <v>6750000</v>
       </c>
     </row>
-    <row r="58" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B58" s="40" t="s">
+    <row r="58" spans="1:4" ht="18" x14ac:dyDescent="0.35">
+      <c r="B58" s="39" t="s">
         <v>59</v>
       </c>
-      <c r="C58" s="41">
+      <c r="C58" s="40">
         <f>C29+C36+C44+C54</f>
         <v>38250000</v>
       </c>
